--- a/excelCfg/ability.xlsx
+++ b/excelCfg/ability.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ability" sheetId="1" r:id="R2b6d6748a462482a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ability" sheetId="1" r:id="R2d832faf39174d0f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5262,74 +5262,182 @@
       </x:c>
     </x:row>
     <x:row r="50" ht="48" customHeight="1">
-      <x:c r="A50" s="4"/>
-      <x:c r="B50" s="4"/>
-      <x:c r="C50" s="4"/>
-      <x:c r="D50" s="4"/>
-      <x:c r="E50" s="4"/>
+      <x:c r="A50" s="4" t="str">
+        <x:v>A9T4</x:v>
+      </x:c>
+      <x:c r="B50" s="4" t="str">
+        <x:v>ANcl</x:v>
+      </x:c>
+      <x:c r="C50" s="4" t="str">
+        <x:v>跟随</x:v>
+      </x:c>
+      <x:c r="D50" s="4" t="str">
+        <x:v>跟随(|cffffcc00T|r)</x:v>
+      </x:c>
+      <x:c r="E50" s="4" t="str">
+        <x:v>立即传送到绑定英雄身边。|n冷却时间：1 秒。</x:v>
+      </x:c>
       <x:c r="F50" s="4"/>
       <x:c r="G50" s="4"/>
-      <x:c r="H50" s="4"/>
+      <x:c r="H50" s="4" t="str">
+        <x:v>T</x:v>
+      </x:c>
       <x:c r="I50" s="4"/>
-      <x:c r="J50" s="5"/>
-      <x:c r="K50" s="5"/>
-      <x:c r="L50" s="5"/>
-      <x:c r="M50" s="5"/>
-      <x:c r="N50" s="5"/>
-      <x:c r="O50" s="5"/>
-      <x:c r="P50" s="5"/>
-      <x:c r="Q50" s="5"/>
-      <x:c r="R50" s="5"/>
-      <x:c r="S50" s="4"/>
-      <x:c r="T50" s="4"/>
-      <x:c r="U50" s="4"/>
-      <x:c r="V50" s="4"/>
-      <x:c r="W50" s="4"/>
-      <x:c r="X50" s="4"/>
-      <x:c r="Y50" s="4"/>
-      <x:c r="Z50" s="4"/>
-      <x:c r="AA50" s="4"/>
+      <x:c r="J50" s="5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K50" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L50" s="5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M50" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N50" s="5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O50" s="5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P50" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q50" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R50" s="5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S50" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T50" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U50" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V50" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W50" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X50" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y50" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z50" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA50" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="AB50" s="4"/>
       <x:c r="AC50" s="4"/>
       <x:c r="AD50" s="4"/>
-      <x:c r="AE50" s="4"/>
-      <x:c r="AF50" s="4"/>
-      <x:c r="AG50" s="4"/>
+      <x:c r="AE50" s="4" t="str">
+        <x:v>channel</x:v>
+      </x:c>
+      <x:c r="AF50" s="4" t="str">
+        <x:v>channel</x:v>
+      </x:c>
+      <x:c r="AG50" s="4" t="str">
+        <x:v>ReplaceableTextures\CommandButtons\BTNScrollOfTownPortal.blp</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="48" customHeight="1">
-      <x:c r="A51" s="4"/>
-      <x:c r="B51" s="4"/>
-      <x:c r="C51" s="4"/>
-      <x:c r="D51" s="4"/>
-      <x:c r="E51" s="4"/>
+      <x:c r="A51" s="4" t="str">
+        <x:v>A9T5</x:v>
+      </x:c>
+      <x:c r="B51" s="4" t="str">
+        <x:v>ANcl</x:v>
+      </x:c>
+      <x:c r="C51" s="4" t="str">
+        <x:v>范围合成</x:v>
+      </x:c>
+      <x:c r="D51" s="4" t="str">
+        <x:v>范围合成(|cffffcc00Y|r)</x:v>
+      </x:c>
+      <x:c r="E51" s="4" t="str">
+        <x:v>指定一个地面区域。范围内每两件同等级、可合成的地面装备会合成为一件随机的下一等级装备。|n范围：300|n施法距离：900|n冷却时间：3 秒。</x:v>
+      </x:c>
       <x:c r="F51" s="4"/>
       <x:c r="G51" s="4"/>
-      <x:c r="H51" s="4"/>
+      <x:c r="H51" s="4" t="str">
+        <x:v>Y</x:v>
+      </x:c>
       <x:c r="I51" s="4"/>
-      <x:c r="J51" s="5"/>
-      <x:c r="K51" s="5"/>
-      <x:c r="L51" s="5"/>
-      <x:c r="M51" s="5"/>
-      <x:c r="N51" s="5"/>
-      <x:c r="O51" s="5"/>
-      <x:c r="P51" s="5"/>
-      <x:c r="Q51" s="5"/>
-      <x:c r="R51" s="5"/>
-      <x:c r="S51" s="4"/>
-      <x:c r="T51" s="4"/>
-      <x:c r="U51" s="4"/>
-      <x:c r="V51" s="4"/>
-      <x:c r="W51" s="4"/>
-      <x:c r="X51" s="4"/>
-      <x:c r="Y51" s="4"/>
-      <x:c r="Z51" s="4"/>
-      <x:c r="AA51" s="4"/>
+      <x:c r="J51" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K51" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L51" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M51" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N51" s="5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O51" s="5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P51" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q51" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R51" s="5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S51" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="T51" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U51" s="4" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="V51" s="4" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="W51" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X51" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Y51" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z51" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA51" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="AB51" s="4"/>
       <x:c r="AC51" s="4"/>
       <x:c r="AD51" s="4"/>
-      <x:c r="AE51" s="4"/>
-      <x:c r="AF51" s="4"/>
-      <x:c r="AG51" s="4"/>
+      <x:c r="AE51" s="4" t="str">
+        <x:v>berserk</x:v>
+      </x:c>
+      <x:c r="AF51" s="4" t="str">
+        <x:v>berserk</x:v>
+      </x:c>
+      <x:c r="AG51" s="4" t="str">
+        <x:v>ReplaceableTextures\CommandButtons\BTNTransmute.blp</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="48" customHeight="1">
       <x:c r="A52" s="4"/>

--- a/excelCfg/ability.xlsx
+++ b/excelCfg/ability.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ability" sheetId="1" r:id="R2d832faf39174d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ability" sheetId="1" r:id="R8163a2aa2d094183"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2344,22 +2344,22 @@
         <x:v>A0E1</x:v>
       </x:c>
       <x:c r="B16" s="4" t="str">
-        <x:v>AHtb</x:v>
+        <x:v>ANcl</x:v>
       </x:c>
       <x:c r="C16" s="4" t="str">
-        <x:v>天眼诛邪</x:v>
+        <x:v>死亡缠绕</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
-        <x:v>天眼诛邪(|cffffcc00Q|r)</x:v>
+        <x:v>死亡缠绕(|cffffcc00Q|r)</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>锁定单体打出高额伤害，对精英与 Boss 的额外伤害由 Lua 继续结算。</x:v>
+        <x:v>向目标投掷死亡缠绕，造成主属性伤害；对自身施放时恢复生命。肉鸽强化可使魂球在敌人间弹射。</x:v>
       </x:c>
       <x:c r="F16" s="4" t="str">
-        <x:v>学习天眼诛邪(|cffffcc00Q|r) - [等级 %d]</x:v>
+        <x:v>学习死亡缠绕(|cffffcc00Q|r) - [等级 %d]</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>锁定单体打出高额伤害，对精英与 Boss 的额外伤害由 Lua 继续结算。</x:v>
+        <x:v>向目标投掷死亡缠绕，造成主属性伤害；对自身施放时恢复生命。肉鸽强化可使魂球在敌人间弹射。</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
         <x:v>Q</x:v>
@@ -2398,7 +2398,7 @@
         <x:v>{ 8, 7, 6 }</x:v>
       </x:c>
       <x:c r="T16" s="4" t="str">
-        <x:v>{ 70, 85, 100 }</x:v>
+        <x:v>{ 60, 75, 90 }</x:v>
       </x:c>
       <x:c r="U16" s="4" t="str">
         <x:v>{ 650, 650, 650 }</x:v>
@@ -2409,20 +2409,30 @@
       <x:c r="W16" s="4" t="str">
         <x:v>{ 0, 0, 0 }</x:v>
       </x:c>
-      <x:c r="X16" s="4"/>
-      <x:c r="Y16" s="4"/>
-      <x:c r="Z16" s="4"/>
-      <x:c r="AA16" s="4"/>
+      <x:c r="X16" s="4" t="str">
+        <x:v>{ 1, 1, 1 }</x:v>
+      </x:c>
+      <x:c r="Y16" s="4" t="str">
+        <x:v>{ 1, 1, 1 }</x:v>
+      </x:c>
+      <x:c r="Z16" s="4" t="str">
+        <x:v>{ 0, 0, 0 }</x:v>
+      </x:c>
+      <x:c r="AA16" s="4" t="str">
+        <x:v>{ 0, 0, 0 }</x:v>
+      </x:c>
       <x:c r="AB16" s="4"/>
-      <x:c r="AC16" s="4" t="str">
-        <x:v>{ 0, 0, 0 }</x:v>
-      </x:c>
-      <x:c r="AD16" s="4" t="str">
-        <x:v>{ 0, 0, 0 }</x:v>
-      </x:c>
-      <x:c r="AE16" s="4"/>
-      <x:c r="AF16" s="4"/>
-      <x:c r="AG16" s="4"/>
+      <x:c r="AC16" s="4"/>
+      <x:c r="AD16" s="4"/>
+      <x:c r="AE16" s="4" t="str">
+        <x:v>{ "deathcoil", "deathcoil", "deathcoil" }</x:v>
+      </x:c>
+      <x:c r="AF16" s="4" t="str">
+        <x:v>deathcoil</x:v>
+      </x:c>
+      <x:c r="AG16" s="4" t="str">
+        <x:v>ui\selectHero\skills\a0e1.blp</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
       <x:c r="A17" s="4" t="str">
@@ -2432,19 +2442,19 @@
         <x:v>ANcl</x:v>
       </x:c>
       <x:c r="C17" s="4" t="str">
-        <x:v>哮天追猎</x:v>
+        <x:v>凛风冲击</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
-        <x:v>哮天追猎(|cffffcc00W|r)</x:v>
+        <x:v>凛风冲击(|cffffcc00W|r)</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>锁定猎物并召出哮天犬追击，召唤与标记由 Lua 处理。</x:v>
+        <x:v>指定地面区域引爆冰霜，造成主属性伤害并冻结普通敌人；Boss 与免控目标改为减速。</x:v>
       </x:c>
       <x:c r="F17" s="4" t="str">
-        <x:v>学习哮天追猎(|cffffcc00W|r) - [等级 %d]</x:v>
+        <x:v>学习凛风冲击(|cffffcc00W|r) - [等级 %d]</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>锁定猎物并召出哮天犬追击，召唤与标记由 Lua 处理。</x:v>
+        <x:v>指定地面区域引爆冰霜，造成主属性伤害并冻结普通敌人；Boss 与免控目标改为减速。</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
         <x:v>W</x:v>
@@ -2480,16 +2490,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S17" s="4" t="str">
-        <x:v>{ 18, 16, 14 }</x:v>
+        <x:v>{ 14, 12, 10 }</x:v>
       </x:c>
       <x:c r="T17" s="4" t="str">
-        <x:v>{ 85, 100, 115 }</x:v>
+        <x:v>{ 80, 95, 110 }</x:v>
       </x:c>
       <x:c r="U17" s="4" t="str">
         <x:v>{ 700, 700, 700 }</x:v>
       </x:c>
       <x:c r="V17" s="4" t="str">
-        <x:v>{ 0, 0, 0 }</x:v>
+        <x:v>{ 300, 300, 300 }</x:v>
       </x:c>
       <x:c r="W17" s="4" t="str">
         <x:v>{ 0, 0, 0 }</x:v>
@@ -2498,7 +2508,7 @@
         <x:v>{ 2, 2, 2 }</x:v>
       </x:c>
       <x:c r="Y17" s="4" t="str">
-        <x:v>{ 0, 0, 0 }</x:v>
+        <x:v>{ 1, 1, 1 }</x:v>
       </x:c>
       <x:c r="Z17" s="4" t="str">
         <x:v>{ 0, 0, 0 }</x:v>
@@ -2506,40 +2516,40 @@
       <x:c r="AA17" s="4" t="str">
         <x:v>{ 0, 0, 0 }</x:v>
       </x:c>
-      <x:c r="AB17" s="4" t="str">
-        <x:v>{ "B0E1", "B0E1", "B0E1" }</x:v>
-      </x:c>
+      <x:c r="AB17" s="4"/>
       <x:c r="AC17" s="4"/>
       <x:c r="AD17" s="4"/>
       <x:c r="AE17" s="4" t="str">
-        <x:v>{ "howlofterror", "howlofterror", "howlofterror" }</x:v>
+        <x:v>{ "berserk", "berserk", "berserk" }</x:v>
       </x:c>
       <x:c r="AF17" s="4" t="str">
-        <x:v>howlofterror</x:v>
-      </x:c>
-      <x:c r="AG17" s="4"/>
+        <x:v>berserk</x:v>
+      </x:c>
+      <x:c r="AG17" s="4" t="str">
+        <x:v>ui\selectHero\skills\a0e2.blp</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
       <x:c r="A18" s="4" t="str">
         <x:v>A0E3</x:v>
       </x:c>
       <x:c r="B18" s="4" t="str">
-        <x:v>Atru</x:v>
+        <x:v>AOcr</x:v>
       </x:c>
       <x:c r="C18" s="4" t="str">
-        <x:v>神目洞察</x:v>
+        <x:v>霜之哀伤·饥渴</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
-        <x:v>神目洞察(|cffffcc00E|r)</x:v>
+        <x:v>霜之哀伤·饥渴(|cffffcc00E|r)</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>提升暴击并揭示周围隐形单位。</x:v>
+        <x:v>普通攻击积攒魂魄，最多 5 层；6 秒未攻击则消退。满层后的下一次攻击触发强化斩击。当前层数显示在技能图标旁，并可在 Buff 栏看到状态图标。</x:v>
       </x:c>
       <x:c r="F18" s="4" t="str">
-        <x:v>学习神目洞察(|cffffcc00E|r) - [等级 %d]</x:v>
+        <x:v>学习霜之哀伤·饥渴(|cffffcc00E|r) - [等级 %d]</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>提升暴击并揭示周围隐形单位。</x:v>
+        <x:v>普通攻击积攒魂魄，最多 5 层；6 秒未攻击则消退。满层后的下一次攻击触发强化斩击。</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
         <x:v>E</x:v>
@@ -2566,59 +2576,71 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P18" s="5" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Q18" s="5" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="R18" s="5" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="S18" s="4" t="str">
-        <x:v>{ 0, 0 }</x:v>
+        <x:v>{ 0, 0, 0 }</x:v>
       </x:c>
       <x:c r="T18" s="4" t="str">
-        <x:v>{ 0, 0 }</x:v>
+        <x:v>{ 0, 0, 0 }</x:v>
       </x:c>
       <x:c r="U18" s="4" t="str">
-        <x:v>{ 600, 600 }</x:v>
-      </x:c>
-      <x:c r="V18" s="4"/>
+        <x:v>{ 0, 0, 0 }</x:v>
+      </x:c>
+      <x:c r="V18" s="4" t="str">
+        <x:v>{ 0, 0, 0 }</x:v>
+      </x:c>
       <x:c r="W18" s="4" t="str">
-        <x:v>{ 3, 3 }</x:v>
-      </x:c>
-      <x:c r="X18" s="4"/>
-      <x:c r="Y18" s="4"/>
-      <x:c r="Z18" s="4"/>
-      <x:c r="AA18" s="4"/>
+        <x:v>{ 0, 0, 0 }</x:v>
+      </x:c>
+      <x:c r="X18" s="4" t="str">
+        <x:v>{ 0, 0, 0 }</x:v>
+      </x:c>
+      <x:c r="Y18" s="4" t="str">
+        <x:v>{ 0, 0, 0 }</x:v>
+      </x:c>
+      <x:c r="Z18" s="4" t="str">
+        <x:v>{ 0, 0, 0 }</x:v>
+      </x:c>
+      <x:c r="AA18" s="4" t="str">
+        <x:v>{ 0, 0, 0 }</x:v>
+      </x:c>
       <x:c r="AB18" s="4"/>
       <x:c r="AC18" s="4"/>
       <x:c r="AD18" s="4"/>
       <x:c r="AE18" s="4"/>
       <x:c r="AF18" s="4"/>
-      <x:c r="AG18" s="4"/>
+      <x:c r="AG18" s="4" t="str">
+        <x:v>ui\selectHero\skills\a0e3.blp</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
       <x:c r="A19" s="4" t="str">
         <x:v>A0E4</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
-        <x:v>AOcr</x:v>
+        <x:v>ANcl</x:v>
       </x:c>
       <x:c r="C19" s="4" t="str">
-        <x:v>司法天威</x:v>
+        <x:v>亡灵大军</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>司法天威(|cffffcc00R|r)</x:v>
+        <x:v>亡灵大军(|cffffcc00R|r)</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>对精英与 Boss 周期性追加额外伤害，具体最大生命值伤害由 Lua 结算。</x:v>
+        <x:v>指定区域召唤食尸鬼协战。冷却：45 / 40 秒；耗魔：120 / 150。军团存在时再次按 R 可献祭最近的一只食尸鬼并恢复生命；献祭治疗受本次召唤的总量上限约束。</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
-        <x:v>学习司法天威(|cffffcc00R|r) - [等级 %d]</x:v>
+        <x:v>学习亡灵大军(|cffffcc00R|r) - [等级 %d]</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>对精英与 Boss 周期性追加额外伤害，具体最大生命值伤害由 Lua 结算。</x:v>
+        <x:v>指定区域召唤食尸鬼协战。冷却：45 / 40 秒；耗魔：120 / 150。军团存在时再次按 R 可献祭最近的一只食尸鬼并恢复生命。</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
         <x:v>R</x:v>
@@ -2659,16 +2681,20 @@
       <x:c r="T19" s="4" t="str">
         <x:v>{ 0, 0 }</x:v>
       </x:c>
-      <x:c r="U19" s="4"/>
-      <x:c r="V19" s="4"/>
+      <x:c r="U19" s="4" t="str">
+        <x:v>{ 700, 700 }</x:v>
+      </x:c>
+      <x:c r="V19" s="4" t="str">
+        <x:v>{ 0, 0 }</x:v>
+      </x:c>
       <x:c r="W19" s="4" t="str">
         <x:v>{ 0, 0 }</x:v>
       </x:c>
       <x:c r="X19" s="4" t="str">
-        <x:v>{ 0, 0 }</x:v>
+        <x:v>{ 2, 2 }</x:v>
       </x:c>
       <x:c r="Y19" s="4" t="str">
-        <x:v>{ 0, 0 }</x:v>
+        <x:v>{ 1, 1 }</x:v>
       </x:c>
       <x:c r="Z19" s="4" t="str">
         <x:v>{ 0, 0 }</x:v>
@@ -2679,9 +2705,15 @@
       <x:c r="AB19" s="4"/>
       <x:c r="AC19" s="4"/>
       <x:c r="AD19" s="4"/>
-      <x:c r="AE19" s="4"/>
-      <x:c r="AF19" s="4"/>
-      <x:c r="AG19" s="4"/>
+      <x:c r="AE19" s="4" t="str">
+        <x:v>{ "berserk", "berserk" }</x:v>
+      </x:c>
+      <x:c r="AF19" s="4" t="str">
+        <x:v>berserk</x:v>
+      </x:c>
+      <x:c r="AG19" s="4" t="str">
+        <x:v>ui\selectHero\skills\a0e4.blp</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
       <x:c r="A20" s="4" t="str">

--- a/excelCfg/ability.xlsx
+++ b/excelCfg/ability.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ability" sheetId="1" r:id="R74b7a7d9aae84cbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ability" sheetId="1" r:id="Re2824428feb0443b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1683,13 +1683,13 @@
         <x:v>贯日箭(|cffffcc00Q|r)</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
-        <x:v>向指定地点射出贯日长箭，对直线上的最多 4 名敌人造成主属性伤害并附加一层日痕。射程：900；宽度：96。</x:v>
+        <x:v>向指定地点射出贯日长箭。箭矢以 1500/秒飞行 900 距离，飞行期间每 0.03 秒对周围 100 范围内的所有敌人造成主属性伤害；同一支箭对同一目标最多命中一次，整次施法最多附加一层日痕。</x:v>
       </x:c>
       <x:c r="F8" s="4" t="str">
         <x:v>学习贯日箭(|cffffcc00Q|r) - [等级 %d]</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
-        <x:v>向指定地点射出贯日长箭，对直线上的最多 4 名敌人造成主属性伤害并附加一层日痕。</x:v>
+        <x:v>向指定地点射出贯日长箭，飞行期间持续伤害箭矢周围 100 范围敌人；整次施法最多附加一层日痕。</x:v>
       </x:c>
       <x:c r="H8" s="4" t="str">
         <x:v>Q</x:v>

--- a/excelCfg/ability.xlsx
+++ b/excelCfg/ability.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ability" sheetId="1" r:id="Re2824428feb0443b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ability" sheetId="1" r:id="Ref3831e797ba4845"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2470,19 +2470,19 @@
         <x:v>ANcl</x:v>
       </x:c>
       <x:c r="C17" s="4" t="str">
-        <x:v>凛风冲击</x:v>
+        <x:v>冰龙卷</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
-        <x:v>凛风冲击(|cffffcc00W|r)</x:v>
+        <x:v>冰龙卷(|cffffcc00W|r)</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>指定地面区域引爆冰霜，造成主属性伤害并冻结普通敌人；Boss 与免控目标改为减速。</x:v>
+        <x:v>在指定地点生成冰龙卷，持续 3 秒。冰龙卷每 0.5 秒对范围内敌人造成主属性魔法伤害，共 6 次。</x:v>
       </x:c>
       <x:c r="F17" s="4" t="str">
-        <x:v>学习凛风冲击(|cffffcc00W|r) - [等级 %d]</x:v>
+        <x:v>学习冰龙卷(|cffffcc00W|r) - [等级 %d]</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>指定地面区域引爆冰霜，造成主属性伤害并冻结普通敌人；Boss 与免控目标改为减速。</x:v>
+        <x:v>在指定地点生成冰龙卷，持续 3 秒。冰龙卷每 0.5 秒对范围内敌人造成主属性魔法伤害，共 6 次。</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
         <x:v>W</x:v>
@@ -2521,7 +2521,7 @@
         <x:v>{ 14, 12, 10 }</x:v>
       </x:c>
       <x:c r="T17" s="4" t="str">
-        <x:v>{ 80, 95, 110 }</x:v>
+        <x:v>{ 0, 0, 0 }</x:v>
       </x:c>
       <x:c r="U17" s="4" t="str">
         <x:v>{ 700, 700, 700 }</x:v>
@@ -2548,10 +2548,10 @@
       <x:c r="AC17" s="4"/>
       <x:c r="AD17" s="4"/>
       <x:c r="AE17" s="4" t="str">
-        <x:v>{ "berserk", "berserk", "berserk" }</x:v>
+        <x:v>{ "channel", "channel", "channel" }</x:v>
       </x:c>
       <x:c r="AF17" s="4" t="str">
-        <x:v>berserk</x:v>
+        <x:v>channel</x:v>
       </x:c>
       <x:c r="AG17" s="4" t="str">
         <x:v>ui\selectHero\skills\a0e2.blp</x:v>
